--- a/data/eval/aff_lived_experience_coverage_v2_layers_20260716_175207.xlsx
+++ b/data/eval/aff_lived_experience_coverage_v2_layers_20260716_175207.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE11"/>
+  <dimension ref="A1:AE31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,6 +1303,1438 @@
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>trigunas</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>two-forms-of-brahman</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Two Forms of Brahman</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>western</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>excessive</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>11</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>I can't stop sorting everything into what I can touch and what I can't. At dinner, I'm barely tasting the food because I'm trying to locate the thing behind it — the part that isn't bread or sauce. My partner says I look like I'm somewhere else, and she's right.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>vitarka, vismaya, rajas, sattva, rati, mati, autsukya, sama, tamas, capalata</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>trigunas</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>two-forms-of-brahman</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Two Forms of Brahman</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>western</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>excessive</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>12</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>In meetings, I keep dismissing what people are actually saying because I'm fixated on something invisible underneath their words. I know it makes me a bad listener. My manager has mentioned it. But the concrete stuff feels like wrapping paper and I can't stop trying to get at what's inside.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>rajas, vismaya, vitarka, capalata, sattva, mati, autsukya, sama, tamas, rati, garva</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>trigunas</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>two-forms-of-brahman</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Two Forms of Brahman</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>western</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>excessive</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>13</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>My brother invited me to his kid's birthday party and I spent the whole time feeling like the balloons, the cake, the screaming children were a thin screen over something else. I couldn't just be there. I kept reaching past everything visible and missing the actual event.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>nirveda, three-gunas-as-daily-veils, rati, sattva, tamas, vismaya, moha, rajas, sama, autsukya, hasa, jadata</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>trigunas</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>two-forms-of-brahman</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Two Forms of Brahman</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>western</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>excessive</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>14</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>I lie in bed at night and my body on the mattress feels like a shell. I can't stop trying to sense what's behind the sensation of the sheets, the weight of my limbs. I lose sleep over it — not anxiously, but because I can't let the physical world just be enough.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>vismaya, vitarka, sama, sattva, nidra, tamas, nirveda, rajas, rati, dhrti, cinta</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>trigunas</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>two-forms-of-brahman</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Two Forms of Brahman</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>western</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>excessive</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>15</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>My friend asked me a simple question — what I wanted for lunch — and I froze because I was caught up in the gap between what lunch is as a thing and what lunch is beyond being a thing. She looked at me like I was broken. It's affecting my daily life now.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>jadata, vismaya, vitarka, tamas, moha, rajas, sama, rajas-projects-tamas-veils-sattva-reveals, sattva, vrida, cinta, hasa</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>trigunas</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>two-forms-of-brahman</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Two Forms of Brahman</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>western</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>excessive</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>I've stopped enjoying hikes because I spend the whole time trying to see through the trees, the rocks, the trail — not past them physically, but into whatever they're an expression of. The defined part of everything has started to feel like an obstacle rather than something to appreciate.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>two-forms-of-brahman</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>vismaya, nirveda, sattva, rajas-projects-tamas-veils-sattva-reveals, rajas, vitarka, rati, two-forms-of-brahman, sama, autsukya, cinta, hasa, moha</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>trigunas</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>two-forms-of-brahman</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Two Forms of Brahman</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>western</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>excessive</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>17</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>At my son's school play, I could see him on stage in his costume, hear his little voice, but I couldn't connect to that layer. I was stuck trying to reach something formless behind the scene. My wife noticed I didn't clap when everyone else did.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>rati, jadata, tamas, moha, rajas-projects-tamas-veils-sattva-reveals, vismaya, harsa, sattva, nirveda, three-gunas-as-daily-veils, sama, hasa, avahittha</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>trigunas</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>two-forms-of-brahman</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Two Forms of Brahman</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>western</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>excessive</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>18</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Every object I look at — my coffee mug, my keyboard, my colleague's face — I immediately see two things: the thing itself and what can't be said about it. It used to feel like insight. Now it's like a compulsion. I can't just use the mug.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>vitarka, vismaya, rajas, sama, sattva, mati, nirveda, capalata, dhrti, tamas, rati</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>trigunas</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>two-forms-of-brahman</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Two Forms of Brahman</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>western</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>excessive</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>19</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>My therapist asked what I'm feeling and all I could say is what I'm not feeling. Not sad, not happy, not numb. I kept ruling things out but couldn't land anywhere positive. She said it sounded exhausting. It is.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>sama, tamas, nirveda, glani, sattva, rati, rajas, vitarka, three-gunas-as-daily-veils, hasa, jadata, vismaya, cinta</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>trigunas</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>two-forms-of-brahman</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Two Forms of Brahman</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>western</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>excessive</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>20</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>When my girlfriend touches my arm, I register her hand, the pressure, the warmth — and then immediately I'm pulled toward whatever is behind the touch that makes it more than skin on skin. I can't stay in the simple moment. She says I feel far away even when I'm right there.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>rati, rajas, vitarka, sama, sattva, autsukya, rajas-projects-tamas-veils-sattva-reveals, vismaya, cinta, moha</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>trigunas</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>two-forms-of-brahman</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Two Forms of Brahman</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>western</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>deficient</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>21</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Everything is just what it is to me. The table is a table. The meeting is a meeting. People talk about sensing something more, something underneath things, and I genuinely don't know what they mean. I just see what's in front of me and that's the whole picture.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Triguṇa — Sattva·Rajas·Tamas, Sthāyībhāvas, Vyabhicārībhāvas</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>trigunas</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>two-forms-of-brahman</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Two Forms of Brahman</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>western</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>deficient</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>22</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>My wife told me she feels something sacred in our home that isn't about the furniture or the walls, and I had nothing to say. I see the furniture. I see the walls. That's what home is for me. Whatever else she's pointing at — I can't find it.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>vismaya, tamas, sattva, jadata, rajas-projects-tamas-veils-sattva-reveals, rati, three-gunas-as-daily-veils, nirveda, visada, moha, sama, vitarka</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>trigunas</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>two-forms-of-brahman</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Two Forms of Brahman</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>western</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>deficient</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>23</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>At the funeral, everyone seemed to sense something beyond the body in the casket — something still present. I only saw the body. I wanted to feel what they felt, but my experience stopped at what was physically there.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>vismaya, tamas, soka, nirveda, sattva, three-gunas-as-daily-veils, jadata, rajas-projects-tamas-veils-sattva-reveals, rati, visada, dainya, sama, moha</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>trigunas</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>two-forms-of-brahman</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Two Forms of Brahman</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>western</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>deficient</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>24</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>When my friend says a sunset is more than just light and atmosphere, I don't get it. I enjoy the colours, sure. But 'more than' — more than what? The colours are the sunset. I've always felt slightly locked out of whatever layer other people access.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>vismaya, nirveda, sattva, rati, tamas, vitarka, rajas-projects-tamas-veils-sattva-reveals, mati, jadata, sama</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>trigunas</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>two-forms-of-brahman</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Two Forms of Brahman</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>western</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>deficient</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>25</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>My morning is shower, coffee, drive, desk. Objects, tasks, surfaces. I sometimes wonder if there's supposed to be something else holding all of that together — some kind of invisible thread — but when I reach for it, there's nothing there. Just the next task.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>rati, tamas, nirveda, vismaya, sattva, utsaha, jadata, rajas, sama, glani, alasya</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>trigunas</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>two-forms-of-brahman</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Two Forms of Brahman</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>western</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>deficient</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>26</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>My neighbour tried to explain why he meditates — something about what's behind his thoughts. I hear the words but I live entirely in my thoughts and what I can touch. The idea that there's a formless something I'm missing doesn't connect to anything in my experience.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>two-forms-of-brahman</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>vismaya, two-forms-of-brahman, rajas-projects-tamas-veils-sattva-reveals, tamas, vibodha, sattva, sama, nirveda, vitarka, mati, rati</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>trigunas</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>two-forms-of-brahman</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Two Forms of Brahman</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>western</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>deficient</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>27</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>At work, I'm effective because I deal with what's measurable and concrete. But in quieter moments — waiting for my daughter at practice — people seem to settle into something I can't locate. I just scroll my phone because the bench, the field, the waiting — that's all there is for me.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>sama, vismaya, tamas, nirveda, sattva, rajas, three-gunas-as-daily-veils, rati, jadata, capalata, hasa, dhrti</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>trigunas</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>two-forms-of-brahman</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Two Forms of Brahman</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>western</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>deficient</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>28</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>My college roommate used to say that describing me was impossible because the real me wasn't my habits or my face. I thought that was nonsense. I am my habits and my face. I've never sensed some undefined version of myself that can't be pinned down.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>vismaya, mati, tamas, dhrti, sattva, sama, nirveda, vitarka, rajas, rati</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>trigunas</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>two-forms-of-brahman</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Two Forms of Brahman</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>western</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>deficient</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>29</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>When my kid asks me what's behind the sky, I say more sky, then space, then nothing. I don't have a sense that there's some other kind of answer — something undefinable. The question ends where the physical stuff ends.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>two-forms-of-brahman</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>vismaya, mati, sattva, two-forms-of-brahman, sama, tamas, nirveda, vitarka, rati, rajas</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>trigunas</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>two-forms-of-brahman</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Two Forms of Brahman</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>western</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>deficient</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>30</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>People at the networking event were making small talk and someone said they could feel the energy of the room, something invisible connecting everyone. I just felt bodies, noise, and too much cologne. If there's a formless layer to a crowded room, it doesn't register for me at all.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>vismaya, nirveda, sattva, tamas, rati, mati, sama, jadata, hasa, vitarka, rajas</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
